--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B9047E-8EE1-4398-8E68-F21A586DC7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B8408E-E390-4783-BBE1-FAC8661CA04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="96">
   <si>
     <t>Client</t>
   </si>
@@ -225,9 +225,6 @@
     <t>MD</t>
   </si>
   <si>
-    <t>Homecare</t>
-  </si>
-  <si>
     <t>Bank</t>
   </si>
   <si>
@@ -310,6 +307,18 @@
   </si>
   <si>
     <t>Derek Janisch</t>
+  </si>
+  <si>
+    <t>Job Types</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Activism Advisory</t>
+  </si>
+  <si>
+    <t>LOB</t>
   </si>
 </sst>
 </file>
@@ -683,31 +692,31 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -722,12 +731,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D4B245-1F68-4AA0-B415-B3823CAF7C5D}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -745,17 +754,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -880,13 +894,13 @@
         <v>43</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -897,10 +911,10 @@
         <v>52</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -921,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
@@ -930,16 +944,16 @@
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R2" t="s">
         <v>24</v>
@@ -948,7 +962,7 @@
         <v>24</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U2" t="s">
         <v>27</v>
@@ -963,19 +977,19 @@
         <v>32</v>
       </c>
       <c r="Y2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z2" t="s">
         <v>39</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AC2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AD2" t="s">
         <v>8</v>
@@ -992,10 +1006,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1016,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
         <v>51</v>
@@ -1025,16 +1039,16 @@
         <v>16</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R3" t="s">
         <v>24</v>
@@ -1043,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U3" t="s">
         <v>27</v>
@@ -1064,13 +1078,13 @@
         <v>39</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AC3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AD3" t="s">
         <v>8</v>
@@ -1090,7 +1104,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1111,7 +1125,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s">
         <v>51</v>
@@ -1120,16 +1134,16 @@
         <v>16</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R4" t="s">
         <v>24</v>
@@ -1138,7 +1152,7 @@
         <v>24</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U4" t="s">
         <v>27</v>
@@ -1153,19 +1167,19 @@
         <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z4" t="s">
         <v>39</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AC4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AD4" t="s">
         <v>8</v>
@@ -1183,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
@@ -1191,9 +1205,10 @@
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -1209,8 +1224,14 @@
       <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1218,13 +1239,19 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
-        <v>65</v>
+      <c r="F2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B8408E-E390-4783-BBE1-FAC8661CA04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDF410F-E426-4183-9C5B-CA780E808BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="93">
   <si>
     <t>Client</t>
   </si>
@@ -231,12 +231,6 @@
     <t>Drew Koecher</t>
   </si>
   <si>
-    <t>FVA</t>
-  </si>
-  <si>
-    <t>Creditor Advisors</t>
-  </si>
-  <si>
     <t>Ayati Arvind</t>
   </si>
   <si>
@@ -258,12 +252,6 @@
     <t>Debtor Advisors</t>
   </si>
   <si>
-    <t>Buyside</t>
-  </si>
-  <si>
-    <t>Rob Oudman</t>
-  </si>
-  <si>
     <t>Michael Birney</t>
   </si>
   <si>
@@ -319,6 +307,9 @@
   </si>
   <si>
     <t>LOB</t>
+  </si>
+  <si>
+    <t>Liability Mgmt</t>
   </si>
 </sst>
 </file>
@@ -362,7 +353,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -370,26 +361,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -397,7 +373,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -692,21 +667,21 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,7 +691,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -731,12 +706,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -754,22 +729,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -779,7 +754,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -894,13 +869,13 @@
         <v>43</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -910,11 +885,11 @@
       <c r="B2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>67</v>
+      <c r="C2" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -935,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
@@ -944,16 +919,16 @@
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="R2" t="s">
         <v>24</v>
@@ -962,7 +937,7 @@
         <v>24</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="U2" t="s">
         <v>27</v>
@@ -977,214 +952,24 @@
         <v>32</v>
       </c>
       <c r="Y2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z2" t="s">
         <v>39</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AD2" t="s">
         <v>8</v>
       </c>
       <c r="AE2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>88</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="U3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V3" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="R4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="U4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" t="s">
-        <v>53</v>
-      </c>
-      <c r="W4" t="s">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1228,7 +1013,7 @@
         <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1239,16 +1024,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G2" t="s">
         <v>44</v>
@@ -1322,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDF410F-E426-4183-9C5B-CA780E808BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE06B52-31BB-41E9-B50D-84E308EF36AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
   <si>
     <t>Client</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Liability Mgmt</t>
+  </si>
+  <si>
+    <t>Chris1 Lord1</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1089,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE06B52-31BB-41E9-B50D-84E308EF36AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C929A39B-207E-45B3-B2B6-6D554DCCCB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="93">
   <si>
     <t>Client</t>
   </si>
@@ -307,9 +307,6 @@
   </si>
   <si>
     <t>LOB</t>
-  </si>
-  <si>
-    <t>Liability Mgmt</t>
   </si>
   <si>
     <t>Chris1 Lord1</t>
@@ -376,7 +373,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,14 +655,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -676,7 +673,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -687,12 +684,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -705,14 +702,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B95DFD-557B-4192-AF4F-0AB1E3FD1F6C}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -725,27 +722,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D4B245-1F68-4AA0-B415-B3823CAF7C5D}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -758,35 +755,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -881,7 +878,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -889,7 +886,7 @@
         <v>52</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
         <v>83</v>
@@ -986,17 +983,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -1019,7 +1016,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1051,17 +1048,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1087,9 +1084,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
@@ -1122,14 +1119,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1140,7 +1137,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>59</v>
       </c>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C929A39B-207E-45B3-B2B6-6D554DCCCB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7780A072-51D0-4C05-AB4C-A11D6AB96236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7780A072-51D0-4C05-AB4C-A11D6AB96236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE7E83-D6C5-45A3-8297-BB802CCA7F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>Client</t>
   </si>
@@ -307,9 +307,6 @@
   </si>
   <si>
     <t>LOB</t>
-  </si>
-  <si>
-    <t>Chris1 Lord1</t>
   </si>
 </sst>
 </file>
@@ -655,14 +652,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -673,7 +670,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -684,12 +681,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -702,14 +699,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B95DFD-557B-4192-AF4F-0AB1E3FD1F6C}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -722,27 +719,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D4B245-1F68-4AA0-B415-B3823CAF7C5D}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -755,35 +752,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="31" max="31" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +875,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -983,17 +980,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -1016,7 +1013,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1048,17 +1045,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1084,9 +1081,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
@@ -1119,14 +1116,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1137,7 +1134,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE7E83-D6C5-45A3-8297-BB802CCA7F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B396E0-0107-4A9A-9E97-A75893633EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5850" yWindow="2220" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -21,17 +21,28 @@
     <sheet name="AddContact" sheetId="3" r:id="rId6"/>
     <sheet name="Contact" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
   <si>
     <t>Client</t>
   </si>
@@ -300,13 +311,16 @@
     <t>Job Types</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
     <t>Activism Advisory</t>
   </si>
   <si>
     <t>LOB</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>CSDN-0000006724</t>
   </si>
 </sst>
 </file>
@@ -651,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -659,7 +673,7 @@
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -670,9 +684,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
         <v>87</v>
@@ -680,13 +694,16 @@
       <c r="C2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -984,7 +1001,7 @@
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -1010,7 +1027,7 @@
         <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,7 +1038,7 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
         <v>72</v>
@@ -1030,7 +1047,7 @@
         <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G2" t="s">
         <v>44</v>

--- a/TestData/LV_TS05_ValidateERPSection.xlsx
+++ b/TestData/LV_TS05_ValidateERPSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B396E0-0107-4A9A-9E97-A75893633EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC720E8D-550A-4832-8AB0-0A799AC75231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="2220" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
   <si>
     <t>Client</t>
   </si>
@@ -272,9 +272,6 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>Indrajeet Singh</t>
-  </si>
-  <si>
     <t>AppName</t>
   </si>
   <si>
@@ -311,6 +308,9 @@
     <t>Job Types</t>
   </si>
   <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
     <t>Activism Advisory</t>
   </si>
   <si>
@@ -320,7 +320,10 @@
     <t>Eric Winthrop</t>
   </si>
   <si>
-    <t>CSDN-0000006724</t>
+    <t>Creditor Advisors</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
   </si>
 </sst>
 </file>
@@ -670,7 +673,7 @@
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -689,13 +692,13 @@
         <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -720,12 +723,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -743,22 +746,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -903,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -924,7 +927,7 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
@@ -936,13 +939,13 @@
         <v>66</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R2" t="s">
         <v>24</v>
@@ -951,7 +954,7 @@
         <v>24</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U2" t="s">
         <v>27</v>
@@ -972,10 +975,10 @@
         <v>39</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC2" t="s">
         <v>71</v>
@@ -1001,7 +1004,7 @@
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -1038,10 +1041,10 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
         <v>92</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>64</v>
